--- a/tests/retriever_test_data/scenarios/retriever_test_scn3.xlsx
+++ b/tests/retriever_test_data/scenarios/retriever_test_scn3.xlsx
@@ -367,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -446,6 +446,9 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
